--- a/Workbook1.xlsx suraj.xlsx
+++ b/Workbook1.xlsx suraj.xlsx
@@ -27,21 +27,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Table15</t>
-  </si>
-  <si>
-    <t>Table 19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cale </t>
-  </si>
-  <si>
-    <t>RELATIVE</t>
-  </si>
-  <si>
-    <t>Absolute</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t xml:space="preserve">Number </t>
+  </si>
+  <si>
+    <t>Student Name</t>
+  </si>
+  <si>
+    <t>Sub 1</t>
+  </si>
+  <si>
+    <t>Sub 2</t>
+  </si>
+  <si>
+    <t>Sub 3</t>
+  </si>
+  <si>
+    <t>Sub 4</t>
+  </si>
+  <si>
+    <t>Sub 5</t>
+  </si>
+  <si>
+    <t>Sub 6</t>
+  </si>
+  <si>
+    <t>Total Marks</t>
+  </si>
+  <si>
+    <t>Harsh singh</t>
+  </si>
+  <si>
+    <t>Uttam singh</t>
+  </si>
+  <si>
+    <t>Kishan singh</t>
+  </si>
+  <si>
+    <t>Madhav singh</t>
+  </si>
+  <si>
+    <t>Mayank singh</t>
+  </si>
+  <si>
+    <t>Vivek singh</t>
+  </si>
+  <si>
+    <t>Sidhharth singh</t>
+  </si>
+  <si>
+    <t>Abhay singh</t>
+  </si>
+  <si>
+    <t>Satya singh</t>
+  </si>
+  <si>
+    <t>Karan singh</t>
   </si>
 </sst>
 </file>
@@ -401,12 +443,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -533,7 +590,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -545,34 +602,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -657,8 +714,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -936,6 +996,26 @@
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I11" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I11" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Number "/>
+    <tableColumn id="2" name="Student Name"/>
+    <tableColumn id="3" name="Sub 1"/>
+    <tableColumn id="4" name="Sub 2"/>
+    <tableColumn id="5" name="Sub 3"/>
+    <tableColumn id="6" name="Sub 4"/>
+    <tableColumn id="7" name="Sub 5"/>
+    <tableColumn id="8" name="Sub 6"/>
+    <tableColumn id="9" name="Total Marks">
+      <calculatedColumnFormula>SUM(C2+D2+E2+F2+G2+H2)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1186,148 +1266,348 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="13.9090909090909" customWidth="1"/>
+    <col min="9" max="9" width="11.6363636363636" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>15</v>
-      </c>
-      <c r="B2">
-        <v>19</v>
-      </c>
-      <c r="C2">
-        <f>A2+B2</f>
-        <v>34</v>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1">
+        <v>73</v>
+      </c>
+      <c r="D2" s="1">
+        <v>35</v>
+      </c>
+      <c r="E2" s="1">
+        <v>94</v>
+      </c>
+      <c r="F2" s="1">
+        <v>67</v>
+      </c>
+      <c r="G2" s="1">
+        <v>91</v>
+      </c>
+      <c r="H2" s="1">
+        <v>71</v>
+      </c>
+      <c r="I2" s="1">
+        <f>SUM(C2:H2)</f>
+        <v>431</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>30</v>
-      </c>
-      <c r="B3">
-        <v>38</v>
-      </c>
-      <c r="C3">
-        <f t="shared" ref="C3:C11" si="0">A3+B3</f>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>97</v>
+      </c>
+      <c r="D3" s="1">
+        <v>90</v>
+      </c>
+      <c r="E3" s="1">
+        <v>83</v>
+      </c>
+      <c r="F3" s="1">
+        <v>76</v>
+      </c>
+      <c r="G3" s="1">
+        <v>69</v>
+      </c>
+      <c r="H3" s="1">
+        <v>62</v>
+      </c>
+      <c r="I3" s="1">
+        <f t="shared" ref="I3:I11" si="0">SUM(C3+D3+E3+F3+G3+H3)</f>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1">
+        <v>92</v>
+      </c>
+      <c r="D4" s="1">
+        <v>85</v>
+      </c>
+      <c r="E4" s="1">
+        <v>78</v>
+      </c>
+      <c r="F4" s="1">
+        <v>71</v>
+      </c>
+      <c r="G4" s="1">
+        <v>64</v>
+      </c>
+      <c r="H4" s="1">
+        <v>57</v>
+      </c>
+      <c r="I4" s="1">
+        <f t="shared" si="0"/>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1">
+        <v>87</v>
+      </c>
+      <c r="D5" s="1">
+        <v>80</v>
+      </c>
+      <c r="E5" s="1">
+        <v>73</v>
+      </c>
+      <c r="F5" s="1">
+        <v>66</v>
+      </c>
+      <c r="G5" s="1">
+        <v>59</v>
+      </c>
+      <c r="H5" s="1">
+        <v>52</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" si="0"/>
+        <v>417</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1">
+        <v>35</v>
+      </c>
+      <c r="D6" s="1">
+        <v>75</v>
+      </c>
+      <c r="E6" s="1">
         <v>68</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>45</v>
-      </c>
-      <c r="B4">
-        <v>57</v>
-      </c>
-      <c r="C4">
-        <f t="shared" si="0"/>
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>60</v>
-      </c>
-      <c r="B5">
-        <v>76</v>
-      </c>
-      <c r="C5">
-        <f t="shared" si="0"/>
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>75</v>
-      </c>
-      <c r="B6">
-        <v>95</v>
-      </c>
-      <c r="C6">
-        <f t="shared" si="0"/>
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>90</v>
-      </c>
-      <c r="B7">
-        <v>114</v>
-      </c>
-      <c r="C7">
-        <f t="shared" si="0"/>
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>105</v>
-      </c>
-      <c r="B8">
-        <v>133</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>238</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>120</v>
-      </c>
-      <c r="B9">
-        <v>152</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="0"/>
-        <v>272</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>135</v>
-      </c>
-      <c r="B10">
-        <v>171</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>150</v>
-      </c>
-      <c r="B11">
-        <v>190</v>
-      </c>
-      <c r="C11">
+      <c r="F6" s="1">
+        <v>61</v>
+      </c>
+      <c r="G6" s="1">
+        <v>54</v>
+      </c>
+      <c r="H6" s="1">
+        <v>47</v>
+      </c>
+      <c r="I6" s="1">
         <f t="shared" si="0"/>
         <v>340</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1">
+        <v>63</v>
+      </c>
+      <c r="F7" s="1">
+        <v>56</v>
+      </c>
+      <c r="G7" s="1">
+        <v>49</v>
+      </c>
+      <c r="H7" s="1">
+        <v>42</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="0"/>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1">
+        <v>58</v>
+      </c>
+      <c r="F8" s="1">
+        <v>51</v>
+      </c>
+      <c r="G8" s="1">
+        <v>44</v>
+      </c>
+      <c r="H8" s="1">
+        <v>37</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="0"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1">
+        <v>15</v>
+      </c>
+      <c r="E9" s="1">
+        <v>53</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46</v>
+      </c>
+      <c r="G9" s="1">
+        <v>39</v>
+      </c>
+      <c r="H9" s="1">
+        <v>32</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="0"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="1">
+        <v>99</v>
+      </c>
+      <c r="D10" s="1">
+        <v>34</v>
+      </c>
+      <c r="E10" s="1">
+        <v>35</v>
+      </c>
+      <c r="F10" s="1">
+        <v>91</v>
+      </c>
+      <c r="G10" s="1">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1">
+        <v>79</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="0"/>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1">
+        <v>80</v>
+      </c>
+      <c r="D11" s="1">
+        <v>80</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>80</v>
+      </c>
+      <c r="G11" s="1">
+        <v>80</v>
+      </c>
+      <c r="H11" s="1">
+        <v>80</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Workbook1.xlsx suraj.xlsx
+++ b/Workbook1.xlsx suraj.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">Number </t>
   </si>
@@ -54,6 +54,18 @@
   </si>
   <si>
     <t>Total Marks</t>
+  </si>
+  <si>
+    <t>Average (%)</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Pass/fail</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
   <si>
     <t>Harsh singh</t>
@@ -443,7 +455,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -452,16 +464,181 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -590,7 +767,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -602,34 +779,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -714,11 +891,65 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -773,7 +1004,19 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="21">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -967,25 +1210,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="10"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstColumn" dxfId="7"/>
+      <tableStyleElement type="lastColumn" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="4"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="totalRow" dxfId="19"/>
+      <tableStyleElement type="firstRowStripe" dxfId="18"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="17"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="16"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="14"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="13"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="12"/>
+      <tableStyleElement type="pageFieldValues" dxfId="11"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -997,9 +1240,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I11" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I11" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M11" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M11" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="13">
     <tableColumn id="1" name="Number "/>
     <tableColumn id="2" name="Student Name"/>
     <tableColumn id="3" name="Sub 1"/>
@@ -1010,6 +1253,18 @@
     <tableColumn id="8" name="Sub 6"/>
     <tableColumn id="9" name="Total Marks">
       <calculatedColumnFormula>SUM(C2+D2+E2+F2+G2+H2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" name="Average (%)" dataDxfId="0">
+      <calculatedColumnFormula>SUM(I2/6)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" name="Rank" dataDxfId="1">
+      <calculatedColumnFormula>RANK(I2,$I$2:$I$11,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" name="Pass/fail" dataDxfId="2">
+      <calculatedColumnFormula>IF(AND(C2&gt;=33,D2&gt;=33,E2&gt;=33,F2&gt;=33,G2&gt;=33,H2&gt;=33),"PASS","FAIL")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" name="Status" dataDxfId="3">
+      <calculatedColumnFormula>IF(AND(C2&gt;=33,D2&gt;=33,E2&gt;=33,F2&gt;=33,G2&gt;=33,H2&gt;=33),"Prmoted","Detained")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1266,341 +1521,514 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="13.9090909090909" customWidth="1"/>
     <col min="9" max="9" width="11.6363636363636" customWidth="1"/>
+    <col min="10" max="10" width="12.8181818181818"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" ht="15.25" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1">
+    <row r="2" ht="15.25" spans="1:13">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="6">
         <v>73</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="6">
         <v>35</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="6">
         <v>94</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="6">
         <v>67</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="6">
         <v>91</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="6">
         <v>71</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="6">
         <f>SUM(C2:H2)</f>
         <v>431</v>
       </c>
+      <c r="J2" s="7">
+        <f t="shared" ref="J2:J11" si="0">SUM(I2/6)</f>
+        <v>71.8333333333333</v>
+      </c>
+      <c r="K2" s="8">
+        <f>RANK(I2,$I$2:$I$11,0)</f>
+        <v>3</v>
+      </c>
+      <c r="L2" s="8" t="str">
+        <f t="shared" ref="L2:L11" si="1">IF(AND(C2&gt;=33,D2&gt;=33,E2&gt;=33,F2&gt;=33,G2&gt;=33,H2&gt;=33),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="M2" s="9" t="str">
+        <f t="shared" ref="M2:M11" si="2">IF(AND(C2&gt;=33,D2&gt;=33,E2&gt;=33,F2&gt;=33,G2&gt;=33,H2&gt;=33),"Prmoted","Detained")</f>
+        <v>Prmoted</v>
+      </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1">
+    <row r="3" ht="15.25" spans="1:13">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="11">
+        <v>97</v>
+      </c>
+      <c r="D3" s="11">
+        <v>90</v>
+      </c>
+      <c r="E3" s="11">
+        <v>83</v>
+      </c>
+      <c r="F3" s="11">
+        <v>76</v>
+      </c>
+      <c r="G3" s="11">
+        <v>69</v>
+      </c>
+      <c r="H3" s="11">
+        <v>62</v>
+      </c>
+      <c r="I3" s="11">
+        <f t="shared" ref="I3:I11" si="3">SUM(C3+D3+E3+F3+G3+H3)</f>
+        <v>477</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" si="0"/>
+        <v>79.5</v>
+      </c>
+      <c r="K3" s="8">
+        <f t="shared" ref="K3:K11" si="4">RANK(I3,$I$2:$I$11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L3" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+      <c r="M3" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>Prmoted</v>
+      </c>
+    </row>
+    <row r="4" ht="15.25" spans="1:13">
+      <c r="A4" s="10">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="11">
+        <v>92</v>
+      </c>
+      <c r="D4" s="11">
+        <v>85</v>
+      </c>
+      <c r="E4" s="11">
+        <v>78</v>
+      </c>
+      <c r="F4" s="11">
+        <v>71</v>
+      </c>
+      <c r="G4" s="11">
+        <v>64</v>
+      </c>
+      <c r="H4" s="11">
+        <v>57</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" si="3"/>
+        <v>447</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="0"/>
+        <v>74.5</v>
+      </c>
+      <c r="K4" s="8">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="L4" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+      <c r="M4" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>Prmoted</v>
+      </c>
+    </row>
+    <row r="5" ht="15.25" spans="1:13">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="11">
+        <v>87</v>
+      </c>
+      <c r="D5" s="11">
+        <v>80</v>
+      </c>
+      <c r="E5" s="11">
+        <v>73</v>
+      </c>
+      <c r="F5" s="11">
+        <v>66</v>
+      </c>
+      <c r="G5" s="11">
+        <v>59</v>
+      </c>
+      <c r="H5" s="11">
+        <v>52</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>417</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="0"/>
+        <v>69.5</v>
+      </c>
+      <c r="K5" s="8">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="L5" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+      <c r="M5" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>Prmoted</v>
+      </c>
+    </row>
+    <row r="6" ht="15.25" spans="1:13">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="11">
+        <v>35</v>
+      </c>
+      <c r="D6" s="11">
+        <v>75</v>
+      </c>
+      <c r="E6" s="11">
+        <v>68</v>
+      </c>
+      <c r="F6" s="11">
+        <v>61</v>
+      </c>
+      <c r="G6" s="11">
+        <v>54</v>
+      </c>
+      <c r="H6" s="11">
+        <v>47</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>340</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="0"/>
+        <v>56.6666666666667</v>
+      </c>
+      <c r="K6" s="8">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="L6" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>PASS</v>
+      </c>
+      <c r="M6" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>Prmoted</v>
+      </c>
+    </row>
+    <row r="7" ht="15.25" spans="1:13">
+      <c r="A7" s="10">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="11">
+        <v>30</v>
+      </c>
+      <c r="D7" s="11">
+        <v>25</v>
+      </c>
+      <c r="E7" s="11">
+        <v>63</v>
+      </c>
+      <c r="F7" s="11">
+        <v>56</v>
+      </c>
+      <c r="G7" s="11">
+        <v>49</v>
+      </c>
+      <c r="H7" s="11">
+        <v>42</v>
+      </c>
+      <c r="I7" s="11">
+        <f t="shared" si="3"/>
+        <v>265</v>
+      </c>
+      <c r="J7" s="12">
+        <f t="shared" si="0"/>
+        <v>44.1666666666667</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="L7" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>FAIL</v>
+      </c>
+      <c r="M7" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>Detained</v>
+      </c>
+    </row>
+    <row r="8" ht="15.25" spans="1:13">
+      <c r="A8" s="10">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="11">
+        <v>25</v>
+      </c>
+      <c r="D8" s="11">
+        <v>20</v>
+      </c>
+      <c r="E8" s="11">
+        <v>58</v>
+      </c>
+      <c r="F8" s="11">
+        <v>51</v>
+      </c>
+      <c r="G8" s="11">
+        <v>44</v>
+      </c>
+      <c r="H8" s="11">
+        <v>37</v>
+      </c>
+      <c r="I8" s="11">
+        <f t="shared" si="3"/>
+        <v>235</v>
+      </c>
+      <c r="J8" s="12">
+        <f t="shared" si="0"/>
+        <v>39.1666666666667</v>
+      </c>
+      <c r="K8" s="8">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="L8" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>FAIL</v>
+      </c>
+      <c r="M8" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>Detained</v>
+      </c>
+    </row>
+    <row r="9" ht="15.25" spans="1:13">
+      <c r="A9" s="10">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="11">
+        <v>20</v>
+      </c>
+      <c r="D9" s="11">
+        <v>15</v>
+      </c>
+      <c r="E9" s="11">
+        <v>53</v>
+      </c>
+      <c r="F9" s="11">
+        <v>46</v>
+      </c>
+      <c r="G9" s="11">
+        <v>39</v>
+      </c>
+      <c r="H9" s="11">
+        <v>32</v>
+      </c>
+      <c r="I9" s="11">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+      <c r="J9" s="12">
+        <f t="shared" si="0"/>
+        <v>34.1666666666667</v>
+      </c>
+      <c r="K9" s="8">
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C3" s="1">
-        <v>97</v>
-      </c>
-      <c r="D3" s="1">
-        <v>90</v>
-      </c>
-      <c r="E3" s="1">
-        <v>83</v>
-      </c>
-      <c r="F3" s="1">
-        <v>76</v>
-      </c>
-      <c r="G3" s="1">
-        <v>69</v>
-      </c>
-      <c r="H3" s="1">
-        <v>62</v>
-      </c>
-      <c r="I3" s="1">
-        <f t="shared" ref="I3:I11" si="0">SUM(C3+D3+E3+F3+G3+H3)</f>
-        <v>477</v>
+      <c r="L9" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>FAIL</v>
+      </c>
+      <c r="M9" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>Detained</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1">
-        <v>92</v>
-      </c>
-      <c r="D4" s="1">
-        <v>85</v>
-      </c>
-      <c r="E4" s="1">
-        <v>78</v>
-      </c>
-      <c r="F4" s="1">
-        <v>71</v>
-      </c>
-      <c r="G4" s="1">
-        <v>64</v>
-      </c>
-      <c r="H4" s="1">
-        <v>57</v>
-      </c>
-      <c r="I4" s="1">
+    <row r="10" ht="15.25" spans="1:13">
+      <c r="A10" s="10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="11">
+        <v>99</v>
+      </c>
+      <c r="D10" s="11">
+        <v>34</v>
+      </c>
+      <c r="E10" s="11">
+        <v>35</v>
+      </c>
+      <c r="F10" s="11">
+        <v>91</v>
+      </c>
+      <c r="G10" s="11">
+        <v>28</v>
+      </c>
+      <c r="H10" s="11">
+        <v>79</v>
+      </c>
+      <c r="I10" s="11">
+        <f t="shared" si="3"/>
+        <v>366</v>
+      </c>
+      <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>447</v>
+        <v>61</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="L10" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>FAIL</v>
+      </c>
+      <c r="M10" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>Detained</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1">
-        <v>87</v>
-      </c>
-      <c r="D5" s="1">
+    <row r="11" ht="15.25" spans="1:13">
+      <c r="A11" s="15">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="16">
         <v>80</v>
       </c>
-      <c r="E5" s="1">
-        <v>73</v>
-      </c>
-      <c r="F5" s="1">
-        <v>66</v>
-      </c>
-      <c r="G5" s="1">
-        <v>59</v>
-      </c>
-      <c r="H5" s="1">
-        <v>52</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="D11" s="16">
+        <v>80</v>
+      </c>
+      <c r="E11" s="16">
+        <v>0</v>
+      </c>
+      <c r="F11" s="16">
+        <v>80</v>
+      </c>
+      <c r="G11" s="16">
+        <v>80</v>
+      </c>
+      <c r="H11" s="16">
+        <v>80</v>
+      </c>
+      <c r="I11" s="16">
+        <f t="shared" si="3"/>
+        <v>400</v>
+      </c>
+      <c r="J11" s="17">
         <f t="shared" si="0"/>
-        <v>417</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1">
+        <v>66.6666666666667</v>
+      </c>
+      <c r="K11" s="8">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1">
-        <v>35</v>
-      </c>
-      <c r="D6" s="1">
-        <v>75</v>
-      </c>
-      <c r="E6" s="1">
-        <v>68</v>
-      </c>
-      <c r="F6" s="1">
-        <v>61</v>
-      </c>
-      <c r="G6" s="1">
-        <v>54</v>
-      </c>
-      <c r="H6" s="1">
-        <v>47</v>
-      </c>
-      <c r="I6" s="1">
-        <f t="shared" si="0"/>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1">
-        <v>30</v>
-      </c>
-      <c r="D7" s="1">
-        <v>25</v>
-      </c>
-      <c r="E7" s="1">
-        <v>63</v>
-      </c>
-      <c r="F7" s="1">
-        <v>56</v>
-      </c>
-      <c r="G7" s="1">
-        <v>49</v>
-      </c>
-      <c r="H7" s="1">
-        <v>42</v>
-      </c>
-      <c r="I7" s="1">
-        <f t="shared" si="0"/>
-        <v>265</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1">
-        <v>58</v>
-      </c>
-      <c r="F8" s="1">
-        <v>51</v>
-      </c>
-      <c r="G8" s="1">
-        <v>44</v>
-      </c>
-      <c r="H8" s="1">
-        <v>37</v>
-      </c>
-      <c r="I8" s="1">
-        <f t="shared" si="0"/>
-        <v>235</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="1">
-        <v>20</v>
-      </c>
-      <c r="D9" s="1">
-        <v>15</v>
-      </c>
-      <c r="E9" s="1">
-        <v>53</v>
-      </c>
-      <c r="F9" s="1">
-        <v>46</v>
-      </c>
-      <c r="G9" s="1">
-        <v>39</v>
-      </c>
-      <c r="H9" s="1">
-        <v>32</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="0"/>
-        <v>205</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="1">
-        <v>99</v>
-      </c>
-      <c r="D10" s="1">
-        <v>34</v>
-      </c>
-      <c r="E10" s="1">
-        <v>35</v>
-      </c>
-      <c r="F10" s="1">
-        <v>91</v>
-      </c>
-      <c r="G10" s="1">
-        <v>28</v>
-      </c>
-      <c r="H10" s="1">
-        <v>79</v>
-      </c>
-      <c r="I10" s="1">
-        <f t="shared" si="0"/>
-        <v>366</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="1">
-        <v>80</v>
-      </c>
-      <c r="D11" s="1">
-        <v>80</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
-        <v>80</v>
-      </c>
-      <c r="G11" s="1">
-        <v>80</v>
-      </c>
-      <c r="H11" s="1">
-        <v>80</v>
-      </c>
-      <c r="I11" s="1">
-        <f t="shared" si="0"/>
-        <v>400</v>
+      <c r="L11" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>FAIL</v>
+      </c>
+      <c r="M11" s="19" t="str">
+        <f t="shared" si="2"/>
+        <v>Detained</v>
       </c>
     </row>
   </sheetData>
